--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>121206378</v>
       </c>
       <c r="B12" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>121206378</v>
       </c>
       <c r="B12" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>121206378</v>
       </c>
       <c r="B12" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>121206378</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>121206378</v>
       </c>
       <c r="B12" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>121206378</v>
       </c>
       <c r="B12" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>82113833</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>114387742</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>119352008</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>120683552</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120682099</v>
+        <v>119871769</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>57431</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,44 +1548,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västerkölen, Dlr</t>
+          <t>Kokällmyren, Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>362646</v>
+        <v>361903</v>
       </c>
       <c r="R9" t="n">
-        <v>6883053</v>
+        <v>6883079</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,22 +1620,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,22 +1650,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120682160</v>
+        <v>120682099</v>
       </c>
       <c r="B10" t="n">
-        <v>78594</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,30 +1678,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1698,13 +1705,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362634</v>
+        <v>362646</v>
       </c>
       <c r="R10" t="n">
-        <v>6882998</v>
+        <v>6883053</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1733,7 +1740,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1743,12 +1750,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Draperade granar i naturskog. Garnlav med apothecier</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,10 +1777,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120683552</v>
+        <v>120682160</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>78594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1791,33 +1793,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1827,10 +1824,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362763</v>
+        <v>362634</v>
       </c>
       <c r="R11" t="n">
-        <v>6883151</v>
+        <v>6882998</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1862,7 +1859,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1872,7 +1869,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Draperade granar i naturskog. Garnlav med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,10 +1901,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206378</v>
+        <v>120683552</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1915,37 +1917,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Västerkölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363234</v>
+        <v>362763</v>
       </c>
       <c r="R12" t="n">
-        <v>6883066</v>
+        <v>6883151</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1969,22 +1983,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,15 +2013,259 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121206378</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>363234</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6883066</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Maria Hindemo</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Maria Hindemo</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121206393</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90646</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>363237</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6883017</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,6 +2267,467 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128821311</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>362158</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6882996</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128821031</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>361972</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6883098</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128821157</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91512</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>362093</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6883101</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128821017</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>361967</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6883096</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2391,7 +2391,7 @@
         <v>128821031</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128821017</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2272,7 +2272,7 @@
         <v>128821311</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>128821031</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128821017</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2272,7 +2272,7 @@
         <v>128821311</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>128821031</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128821017</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2391,7 +2391,7 @@
         <v>128821031</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128821017</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2272,7 +2272,7 @@
         <v>128821311</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>128821031</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128821017</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2272,7 +2272,7 @@
         <v>128821311</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>128821031</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128821017</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>128821157</v>
       </c>
       <c r="B17" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2522,14 +2522,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102713332</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119352037</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206393</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114387775</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682160</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128821017</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128821031</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,6 +1633,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121898927</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1713,6 +1758,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82113833</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114387742</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1938,6 +1993,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119352008</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2057,6 +2117,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683552</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2164,6 +2229,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206319</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2283,6 +2353,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128821311</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2404,6 +2479,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871769</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2515,6 +2595,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172331</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2630,6 +2715,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820996</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2748,8 +2838,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79128510</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>